--- a/Excel/RecipesConfig.xlsx
+++ b/Excel/RecipesConfig.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="22.75" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -501,12 +501,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>recipe1</t>
+          <t>recipe_carrot_soup</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>胡萝卜汤</t>
+          <t>胡萝卜暖汤</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,22 +528,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>recipe2</t>
+          <t>recipe_mushroom_skewer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>炖肉</t>
+          <t>迷雾蘑菇串</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"ingredient_meat":"2","ingredient_salt":"1"}</t>
+          <t>{"ingredient_mushroom":"3","ingredient_salt":"1"}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[food_meat_stew]</t>
+          <t>[food_mushroom_skewer]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -555,27 +555,223 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>recipe3</t>
+          <t>recipe_lotus_crisp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>生命药水</t>
+          <t>莲藕脆片</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"ingredient_carrot":"1","ingredient_salt":"1"}</t>
+          <t>{"ingredient_lotus_root":"3","ingredient_salt":"1"}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[item_potion_red]</t>
+          <t>[food_lotus_crisp]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>recipe_spiced_egg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>香料煎蛋</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{"ingredient_egg":"2","ingredient_spice":"1"}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[food_spiced_egg]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>recipe_wheat_cake</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>麦香烤饼</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{"ingredient_wheat":"2","ingredient_honey":"1"}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[food_wheat_cake]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>recipe_fish_rice</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>河鲜饭团</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{"ingredient_fish":"1","ingredient_rice":"2","ingredient_salt":"1"}</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[food_fish_rice]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>recipe_honey_milk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>蜂蜜热奶</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{"ingredient_milk":"2","ingredient_honey":"1"}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[food_honey_milk]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>recipe_meat_stew</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>秘境炖肉</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{"ingredient_meat":"2","ingredient_carrot":"1","ingredient_spice":"1"}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[food_meat_stew]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>recipe_maze_bento</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>探险便当</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{"ingredient_rice":"2","ingredient_meat":"1","ingredient_egg":"1","ingredient_carrot":"1"}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[food_maze_bento]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>recipe_feast_platter</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>迷宫丰收拼盘</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>{"ingredient_meat":"2","ingredient_fish":"2","ingredient_mushroom":"2","ingredient_spice":"1","ingredient_honey":"1"}</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[food_feast_platter]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>END</t>
         </is>
       </c>
     </row>
